--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0086.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0086.xlsx
@@ -29241,7 +29241,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Không, đưa ta về ████ đi...!</t>
+          <t>Không, đưa tao về ████ đi...!</t>
         </is>
       </c>
     </row>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>QUAY LẠI NÀO, NẮM LẤY TAY Ta!</t>
+          <t>QUAY LẠI NÀO, NẮM LẤY TAY TAO!</t>
         </is>
       </c>
     </row>
